--- a/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_DP/results.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_DP/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.73 ± 0.09</t>
+          <t>0.72 ± 0.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.57 ± 0.12</t>
+          <t>0.58 ± 0.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.61 ± 0.09</t>
+          <t>0.65 ± 0.10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.22</t>
+          <t>0.49 ± 0.25</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.71 ± 0.28</t>
+          <t>0.79 ± 0.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.60 ± 0.42</t>
+          <t>0.58 ± 0.43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
